--- a/output/pdf_financials_xlsx/WPK.xlsx
+++ b/output/pdf_financials_xlsx/WPK.xlsx
@@ -5623,52 +5623,52 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.441</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>-0.426</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>-0.641</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>-1.208</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>-0.029</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.596</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>-2.264</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>-0.524</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>-0.972</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.361</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>-3.174</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="93">
@@ -10180,7 +10180,11 @@
           <t>Reserves 23</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11702,7 +11706,11 @@
           <t>Reserves 25</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -20414,7 +20422,11 @@
           <t>Reserves 24</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -25174,7 +25186,11 @@
           <t>Reserves 22</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -28188,7 +28204,11 @@
           <t>Reserves 21</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E222" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/WPK.xlsx
+++ b/output/pdf_financials_xlsx/WPK.xlsx
@@ -2082,49 +2082,49 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>25.061</v>
+        <v>2.091</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>26.789</v>
+        <v>2.049</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>26.151</v>
+        <v>1.261</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>27.481</v>
+        <v>0.45</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>31.657</v>
+        <v>0.549</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>32.836</v>
+        <v>0.602</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>35.054</v>
+        <v>0.666</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>38.565</v>
+        <v>0.632</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>41.143</v>
+        <v>0.511</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>44.31</v>
+        <v>0.777</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>45.604</v>
+        <v>1.66</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>47.688</v>
+        <v>1.698</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>47.906</v>
+        <v>1.636</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>52.972</v>
+        <v>1.586</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>55.417</v>
+        <v>1.378</v>
       </c>
     </row>
     <row r="29">
@@ -2139,49 +2139,49 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>100.501</v>
+        <v>77.53100000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>117.934</v>
+        <v>93.194</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>128.517</v>
+        <v>103.627</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>131.49</v>
+        <v>104.459</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>146.252</v>
+        <v>115.144</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>179.771</v>
+        <v>147.537</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>192.398</v>
+        <v>158.01</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>198.132</v>
+        <v>160.199</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>187.396</v>
+        <v>146.764</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>195.57</v>
+        <v>152.037</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>186.304</v>
+        <v>142.36</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>215.36</v>
+        <v>169.37</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>223.281</v>
+        <v>177.011</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>235.336</v>
+        <v>183.95</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>227.651</v>
+        <v>173.612</v>
       </c>
     </row>
     <row r="30">
@@ -2196,49 +2196,49 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>17.34447510617992</v>
+        <v>13.38030964325963</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>18.08628920825135</v>
+        <v>14.29217728961772</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>19.17940896432953</v>
+        <v>15.4649160247016</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>18.39352834287585</v>
+        <v>14.61228669228434</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>18.58929220569581</v>
+        <v>14.63532438347946</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>22.55117798108055</v>
+        <v>18.50761883615645</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>23.39094406053503</v>
+        <v>19.21019486171966</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>22.34300960560413</v>
+        <v>18.06536953045534</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>21.06422703090348</v>
+        <v>16.49699148308138</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>22.38045049282308</v>
+        <v>17.39866314658354</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>18.5933249101292</v>
+        <v>14.20766990620702</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>18.23334036048438</v>
+        <v>14.33962136355516</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>19.56190911743138</v>
+        <v>15.50814039163944</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>20.80971266121081</v>
+        <v>16.26587791085822</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>20.22811059703097</v>
+        <v>15.42643228877422</v>
       </c>
     </row>
     <row r="31">
@@ -6022,49 +6022,49 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>2.091</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>2.049</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.261</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.549</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.602</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.632</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>1.698</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>1.636</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>1.586</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>1.378</v>
       </c>
     </row>
     <row r="101">
@@ -36758,7 +36758,11 @@
           <t>Amortization - intangible assets 16</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -39216,7 +39220,11 @@
           <t>Amortization - intangible assets 18</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -42496,7 +42504,11 @@
           <t>Amortization - intangible assets 17</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -44554,7 +44566,11 @@
           <t>Amortization - intangible assets 15</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WPK.xlsx
+++ b/output/pdf_financials_xlsx/WPK.xlsx
@@ -2732,19 +2732,19 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>11.922</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>16.576</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>15.27</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>18.322</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>16.604</v>
       </c>
     </row>
     <row r="41">
@@ -2787,19 +2787,19 @@
         <v>141.855</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>177.382</v>
+        <v>189.304</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>204.04</v>
+        <v>220.616</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>207.355</v>
+        <v>222.625</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>220.201</v>
+        <v>238.523</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>217.099</v>
+        <v>233.703</v>
       </c>
     </row>
     <row r="42">
@@ -3172,19 +3172,19 @@
         <v>4.495</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>16.527</v>
+        <v>4.605</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>9.175000000000001</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>15.049</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>15.459</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>18.38</v>
+        <v>1.776</v>
       </c>
     </row>
     <row r="49">
@@ -3632,31 +3632,31 @@
         <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>770.167</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>818.2910000000001</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>883.9640000000001</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>958.115</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>1042.393</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>1079.742</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>1143.34</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>1269.085</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>1349.114</v>
       </c>
     </row>
     <row r="57">
@@ -3687,31 +3687,31 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>361.02</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>395.302</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>429.529</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>468.848</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>527.146</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>561.152</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>599.953</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>646.419</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>691.476</v>
       </c>
     </row>
     <row r="58">
@@ -4075,28 +4075,28 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>36.123</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>39.146</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>34.96</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>63.789</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>65.285</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>48.927</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>64.03700000000001</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>64.005</v>
       </c>
     </row>
     <row r="65">
@@ -4240,28 +4240,28 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>27.547</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>24.541</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>28.562</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>26.614</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>35.776</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>38.43</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>186.181</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>68.96899999999999</v>
       </c>
     </row>
     <row r="68">
@@ -4295,28 +4295,28 @@
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>63.67</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>63.687</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>63.522</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>90.40300000000001</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>101.061</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>87.357</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>250.218</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0</v>
+        <v>132.974</v>
       </c>
     </row>
     <row r="69">
@@ -4680,28 +4680,28 @@
         <v>78.02200000000001</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>65.32299999999999</v>
+        <v>1.653</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>73.16800000000001</v>
+        <v>9.481</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>71.535</v>
+        <v>8.013</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>97.03700000000001</v>
+        <v>6.634</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>124.724</v>
+        <v>23.663</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>93.946</v>
+        <v>6.589</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>264.935</v>
+        <v>14.717</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>136.112</v>
+        <v>3.138</v>
       </c>
     </row>
     <row r="76">
@@ -6517,7 +6517,7 @@
         <v>0</v>
       </c>
       <c r="P108" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q108" s="3" t="n">
         <v>0</v>
@@ -6934,49 +6934,49 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.252</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.462</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.745</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.861</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.699</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.303</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.43</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.575</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.378</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.122</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.245</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.336</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.462</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-0.9389999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7258,10 +7258,10 @@
         <v>0</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-94.512</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-80.34399999999999</v>
       </c>
     </row>
     <row r="122">
@@ -8878,7 +8878,11 @@
           <t>Intangible assets and goodwill 16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -10994,7 +10998,11 @@
           <t>Intangible assets and goodwill 18</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -36844,7 +36852,11 @@
           <t>Impairment loss on goodwill 16</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -38168,7 +38180,11 @@
           <t>Acquisition of intangible assets 16</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -38532,7 +38548,11 @@
           <t>Repurchase of common shares 23</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -39310,7 +39330,11 @@
           <t>Impairment loss on goodwill 18</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -39842,7 +39866,11 @@
           <t>Acquisition of intangible assets 18</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -40182,7 +40210,11 @@
           <t>Repurchase of common shares 25</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -43074,7 +43106,11 @@
           <t>Acquisition of intangible assets 17</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -45222,7 +45258,11 @@
           <t>Acquisition of intangible assets 15</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
